--- a/downloads/indicadores/BCMM/BCMM_datos.xlsx
+++ b/downloads/indicadores/BCMM/BCMM_datos.xlsx
@@ -507,7 +507,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>URL del boletín / serie: https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226 · Fecha de publicación: 27 de julio de 2026</t>
+          <t>URL del boletín / serie: https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf · Fecha de publicación: 27 de julio de 2026</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L7" s="7" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="K55" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L55" s="7" t="inlineStr">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="K59" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L59" s="7" t="inlineStr">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="K65" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L65" s="7" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="K66" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="K67" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L67" s="7" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="K68" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="K70" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L71" s="7" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="K72" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L73" s="7" t="inlineStr">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="K74" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L75" s="7" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="K76" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="K77" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L77" s="7" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="K79" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L79" s="7" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="K80" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L80" s="4" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="K81" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L81" s="7" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="K83" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L83" s="7" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="K85" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="K87" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L87" s="7" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="K89" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L89" s="7" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="K90" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="K91" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L91" s="7" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="K93" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L93" s="7" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="K94" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="K95" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="K98" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="K99" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L99" s="7" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L101" s="7" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="K102" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="K103" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L103" s="7" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
@@ -6364,7 +6364,7 @@
       </c>
       <c r="K105" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L105" s="7" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="K107" s="7" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/comext_o/balcom_o2026_07.pdf</t>
         </is>
       </c>
       <c r="L107" s="7" t="inlineStr">
